--- a/교육자료/양식/_담당자용/03_진도표.xlsx
+++ b/교육자료/양식/_담당자용/03_진도표.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -488,7 +488,6 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -501,7 +500,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>※ 인쇄해서 손으로 체크해도 됩니다. 이름 칸은 직접 채우세요. (인원 5명 기준 — 바꾸려면 이 파일의 PEOPLE 값 수정)</t>
+          <t>※ 인쇄해서 손으로 체크해도 됩니다. 이름 칸은 직접 채우세요. (인원 4명 기준 — 바꾸려면 이 파일의 PEOPLE 값 수정)</t>
         </is>
       </c>
     </row>
@@ -539,11 +538,6 @@
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>이름 4</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>이름 5</t>
         </is>
       </c>
     </row>
@@ -565,7 +559,6 @@
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="4" t="n">
@@ -585,7 +578,6 @@
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="4" t="n">
@@ -605,7 +597,6 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="4" t="n">
@@ -625,7 +616,6 @@
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="4" t="n">
@@ -645,7 +635,6 @@
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -665,7 +654,6 @@
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="4" t="n">
@@ -685,7 +673,6 @@
       <c r="E11" s="6" t="n"/>
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="4" t="n">
@@ -705,7 +692,6 @@
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="4" t="n">
@@ -725,7 +711,6 @@
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -745,7 +730,6 @@
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="4" t="n">
@@ -765,7 +749,6 @@
       <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="4" t="n">
@@ -785,7 +768,6 @@
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="4" t="n">
@@ -805,7 +787,6 @@
       <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="4" t="n">
@@ -825,7 +806,6 @@
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -845,7 +825,6 @@
       <c r="E19" s="6" t="n"/>
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -865,7 +844,6 @@
       <c r="E20" s="6" t="n"/>
       <c r="F20" s="6" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -885,7 +863,6 @@
       <c r="E21" s="6" t="n"/>
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -905,7 +882,6 @@
       <c r="E22" s="6" t="n"/>
       <c r="F22" s="6" t="n"/>
       <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -925,7 +901,6 @@
       <c r="E23" s="6" t="n"/>
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="4" t="n">
@@ -945,7 +920,6 @@
       <c r="E24" s="6" t="n"/>
       <c r="F24" s="6" t="n"/>
       <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="4" t="n">
@@ -965,7 +939,6 @@
       <c r="E25" s="6" t="n"/>
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
